--- a/Team-Data/2012-13/4-10-2012-13.xlsx
+++ b/Team-Data/2012-13/4-10-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,28 +728,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F2" t="n">
         <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>0.544</v>
+        <v>0.538</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
       </c>
       <c r="I2" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="J2" t="n">
-        <v>80.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.465</v>
+        <v>0.464</v>
       </c>
       <c r="L2" t="n">
         <v>8.699999999999999</v>
@@ -700,7 +767,7 @@
         <v>19.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.713</v>
+        <v>0.71</v>
       </c>
       <c r="R2" t="n">
         <v>9.1</v>
@@ -712,10 +779,10 @@
         <v>40.6</v>
       </c>
       <c r="U2" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="V2" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W2" t="n">
         <v>8</v>
@@ -724,22 +791,22 @@
         <v>4.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z2" t="n">
         <v>18.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>97.90000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -754,10 +821,10 @@
         <v>10</v>
       </c>
       <c r="AI2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK2" t="n">
         <v>6</v>
@@ -775,16 +842,16 @@
         <v>28</v>
       </c>
       <c r="AP2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR2" t="n">
         <v>27</v>
       </c>
       <c r="AS2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT2" t="n">
         <v>24</v>
@@ -802,7 +869,7 @@
         <v>22</v>
       </c>
       <c r="AY2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ2" t="n">
         <v>3</v>
@@ -811,7 +878,7 @@
         <v>25</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
         <v>13</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E3" t="n">
         <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G3" t="n">
-        <v>0.513</v>
+        <v>0.519</v>
       </c>
       <c r="H3" t="n">
         <v>49</v>
@@ -876,7 +943,7 @@
         <v>0.356</v>
       </c>
       <c r="O3" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P3" t="n">
         <v>21.2</v>
@@ -885,22 +952,22 @@
         <v>0.776</v>
       </c>
       <c r="R3" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="S3" t="n">
         <v>31.4</v>
       </c>
       <c r="T3" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="U3" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="V3" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X3" t="n">
         <v>4.6</v>
@@ -915,22 +982,22 @@
         <v>19.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>96.2</v>
+        <v>96.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
         <v>16</v>
       </c>
       <c r="AF3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG3" t="n">
         <v>15</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>16</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
@@ -939,7 +1006,7 @@
         <v>17</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK3" t="n">
         <v>7</v>
@@ -951,10 +1018,10 @@
         <v>26</v>
       </c>
       <c r="AN3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP3" t="n">
         <v>19</v>
@@ -972,13 +1039,13 @@
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AV3" t="n">
         <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX3" t="n">
         <v>21</v>
@@ -987,16 +1054,16 @@
         <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB3" t="n">
         <v>19</v>
       </c>
       <c r="BC3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -1025,19 +1092,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F4" t="n">
         <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>0.59</v>
+        <v>0.584</v>
       </c>
       <c r="H4" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I4" t="n">
         <v>35.7</v>
@@ -1055,25 +1122,25 @@
         <v>21.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.356</v>
+        <v>0.355</v>
       </c>
       <c r="O4" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P4" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.735</v>
+        <v>0.733</v>
       </c>
       <c r="R4" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S4" t="n">
         <v>30.2</v>
       </c>
       <c r="T4" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U4" t="n">
         <v>20.3</v>
@@ -1097,13 +1164,13 @@
         <v>21.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
@@ -1121,34 +1188,34 @@
         <v>26</v>
       </c>
       <c r="AJ4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK4" t="n">
         <v>16</v>
       </c>
       <c r="AL4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM4" t="n">
         <v>8</v>
       </c>
       <c r="AN4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP4" t="n">
         <v>7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR4" t="n">
         <v>5</v>
       </c>
       <c r="AS4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT4" t="n">
         <v>10</v>
@@ -1157,10 +1224,10 @@
         <v>28</v>
       </c>
       <c r="AV4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX4" t="n">
         <v>17</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1342,7 +1409,7 @@
         <v>5</v>
       </c>
       <c r="AW5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX5" t="n">
         <v>6</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -1467,10 +1534,10 @@
         <v>0.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="AE6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF6" t="n">
         <v>12</v>
@@ -1479,7 +1546,7 @@
         <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI6" t="n">
         <v>27</v>
@@ -1524,22 +1591,22 @@
         <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ6" t="n">
         <v>11</v>
       </c>
       <c r="BA6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC6" t="n">
         <v>14</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E7" t="n">
         <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G7" t="n">
-        <v>0.308</v>
+        <v>0.312</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
@@ -1589,19 +1656,19 @@
         <v>36.5</v>
       </c>
       <c r="J7" t="n">
-        <v>84.2</v>
+        <v>84.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0.434</v>
+        <v>0.433</v>
       </c>
       <c r="L7" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M7" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0.347</v>
+        <v>0.349</v>
       </c>
       <c r="O7" t="n">
         <v>17</v>
@@ -1616,40 +1683,40 @@
         <v>12.3</v>
       </c>
       <c r="S7" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="T7" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="U7" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V7" t="n">
         <v>14.1</v>
       </c>
       <c r="W7" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AA7" t="n">
         <v>19.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>96.8</v>
+        <v>96.7</v>
       </c>
       <c r="AC7" t="n">
         <v>-4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE7" t="n">
         <v>27</v>
@@ -1667,13 +1734,13 @@
         <v>19</v>
       </c>
       <c r="AJ7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK7" t="n">
         <v>29</v>
       </c>
       <c r="AL7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM7" t="n">
         <v>16</v>
@@ -1688,7 +1755,7 @@
         <v>14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR7" t="n">
         <v>7</v>
@@ -1700,10 +1767,10 @@
         <v>23</v>
       </c>
       <c r="AU7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW7" t="n">
         <v>16</v>
@@ -1715,16 +1782,16 @@
         <v>29</v>
       </c>
       <c r="AZ7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB7" t="n">
         <v>17</v>
       </c>
       <c r="BC7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -1753,22 +1820,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E8" t="n">
         <v>38</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G8" t="n">
-        <v>0.487</v>
+        <v>0.494</v>
       </c>
       <c r="H8" t="n">
         <v>48.7</v>
       </c>
       <c r="I8" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="J8" t="n">
         <v>84</v>
@@ -1801,13 +1868,13 @@
         <v>32.6</v>
       </c>
       <c r="T8" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U8" t="n">
         <v>23.2</v>
       </c>
       <c r="V8" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W8" t="n">
         <v>7.9</v>
@@ -1816,22 +1883,22 @@
         <v>5.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z8" t="n">
         <v>20.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AB8" t="n">
-        <v>101.1</v>
+        <v>101.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE8" t="n">
         <v>17</v>
@@ -1855,7 +1922,7 @@
         <v>9</v>
       </c>
       <c r="AL8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM8" t="n">
         <v>12</v>
@@ -1891,10 +1958,10 @@
         <v>17</v>
       </c>
       <c r="AX8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ8" t="n">
         <v>23</v>
@@ -1903,7 +1970,7 @@
         <v>24</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC8" t="n">
         <v>17</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F9" t="n">
         <v>24</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H9" t="n">
         <v>48.5</v>
@@ -1959,7 +2026,7 @@
         <v>0.478</v>
       </c>
       <c r="L9" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M9" t="n">
         <v>18.5</v>
@@ -1968,13 +2035,13 @@
         <v>0.343</v>
       </c>
       <c r="O9" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P9" t="n">
         <v>26.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.697</v>
+        <v>0.698</v>
       </c>
       <c r="R9" t="n">
         <v>13.3</v>
@@ -1983,7 +2050,7 @@
         <v>31.5</v>
       </c>
       <c r="T9" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="U9" t="n">
         <v>24.4</v>
@@ -2004,16 +2071,16 @@
         <v>20.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>105.8</v>
+        <v>105.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE9" t="n">
         <v>4</v>
@@ -2034,7 +2101,7 @@
         <v>2</v>
       </c>
       <c r="AK9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL9" t="n">
         <v>20</v>
@@ -2058,7 +2125,7 @@
         <v>1</v>
       </c>
       <c r="AS9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT9" t="n">
         <v>3</v>
@@ -2067,7 +2134,7 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW9" t="n">
         <v>2</v>
@@ -2079,13 +2146,13 @@
         <v>28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA9" t="n">
         <v>4</v>
       </c>
       <c r="BB9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC9" t="n">
         <v>5</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F10" t="n">
         <v>52</v>
       </c>
       <c r="G10" t="n">
-        <v>0.342</v>
+        <v>0.333</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J10" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L10" t="n">
         <v>6.2</v>
@@ -2147,37 +2214,37 @@
         <v>17.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O10" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="P10" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.696</v>
+        <v>0.697</v>
       </c>
       <c r="R10" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T10" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U10" t="n">
         <v>21.2</v>
       </c>
       <c r="V10" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="W10" t="n">
         <v>6.8</v>
       </c>
       <c r="X10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="n">
         <v>5.8</v>
@@ -2186,28 +2253,28 @@
         <v>19.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>94.40000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>-4.4</v>
+        <v>-4.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
         <v>23</v>
@@ -2219,25 +2286,25 @@
         <v>19</v>
       </c>
       <c r="AL10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO10" t="n">
         <v>23</v>
       </c>
       <c r="AP10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ10" t="n">
         <v>29</v>
       </c>
       <c r="AR10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS10" t="n">
         <v>20</v>
@@ -2249,28 +2316,28 @@
         <v>22</v>
       </c>
       <c r="AV10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX10" t="n">
         <v>16</v>
       </c>
       <c r="AY10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ10" t="n">
         <v>13</v>
       </c>
       <c r="BA10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB10" t="n">
         <v>23</v>
       </c>
       <c r="BC10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -2377,10 +2444,10 @@
         <v>0.9</v>
       </c>
       <c r="AD11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE11" t="n">
         <v>9</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>10</v>
       </c>
       <c r="AF11" t="n">
         <v>10</v>
@@ -2404,7 +2471,7 @@
         <v>8</v>
       </c>
       <c r="AM11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN11" t="n">
         <v>1</v>
@@ -2419,7 +2486,7 @@
         <v>3</v>
       </c>
       <c r="AR11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
@@ -2431,7 +2498,7 @@
         <v>14</v>
       </c>
       <c r="AV11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW11" t="n">
         <v>26</v>
@@ -2440,13 +2507,13 @@
         <v>26</v>
       </c>
       <c r="AY11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ11" t="n">
         <v>28</v>
       </c>
       <c r="BA11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB11" t="n">
         <v>9</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>11</v>
@@ -2607,7 +2674,7 @@
         <v>8</v>
       </c>
       <c r="AT12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU12" t="n">
         <v>5</v>
@@ -2616,13 +2683,13 @@
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX12" t="n">
         <v>27</v>
       </c>
       <c r="AY12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
         <v>16</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>4.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="n">
         <v>8</v>
@@ -2753,13 +2820,13 @@
         <v>8</v>
       </c>
       <c r="AH13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
       </c>
       <c r="AJ13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK13" t="n">
         <v>27</v>
@@ -2795,7 +2862,7 @@
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW13" t="n">
         <v>23</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -2845,28 +2912,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E14" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F14" t="n">
         <v>26</v>
       </c>
       <c r="G14" t="n">
-        <v>0.667</v>
+        <v>0.662</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J14" t="n">
         <v>80.59999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.479</v>
+        <v>0.477</v>
       </c>
       <c r="L14" t="n">
         <v>7.6</v>
@@ -2875,13 +2942,13 @@
         <v>21.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0.359</v>
+        <v>0.357</v>
       </c>
       <c r="O14" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P14" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q14" t="n">
         <v>0.712</v>
@@ -2890,40 +2957,40 @@
         <v>11.4</v>
       </c>
       <c r="S14" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T14" t="n">
         <v>41.4</v>
       </c>
       <c r="U14" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="V14" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W14" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y14" t="n">
         <v>4.2</v>
       </c>
       <c r="Z14" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AA14" t="n">
         <v>21</v>
       </c>
-      <c r="AA14" t="n">
-        <v>20.9</v>
-      </c>
       <c r="AB14" t="n">
-        <v>101.2</v>
+        <v>101.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
@@ -2938,22 +3005,22 @@
         <v>26</v>
       </c>
       <c r="AI14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
         <v>25</v>
       </c>
       <c r="AK14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM14" t="n">
         <v>9</v>
       </c>
       <c r="AN14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO14" t="n">
         <v>16</v>
@@ -2962,7 +3029,7 @@
         <v>9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR14" t="n">
         <v>15</v>
@@ -2977,7 +3044,7 @@
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2986,16 +3053,16 @@
         <v>7</v>
       </c>
       <c r="AY14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB14" t="n">
         <v>8</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>7</v>
       </c>
       <c r="BC14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -3027,46 +3094,46 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E15" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F15" t="n">
         <v>37</v>
       </c>
       <c r="G15" t="n">
-        <v>0.532</v>
+        <v>0.526</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J15" t="n">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.46</v>
+        <v>0.458</v>
       </c>
       <c r="L15" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O15" t="n">
         <v>19</v>
       </c>
       <c r="P15" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="R15" t="n">
         <v>11.5</v>
@@ -3075,7 +3142,7 @@
         <v>33.1</v>
       </c>
       <c r="T15" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="U15" t="n">
         <v>22.2</v>
@@ -3090,7 +3157,7 @@
         <v>5.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z15" t="n">
         <v>18</v>
@@ -3099,16 +3166,16 @@
         <v>22.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.2</v>
+        <v>102.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF15" t="n">
         <v>14</v>
@@ -3120,7 +3187,7 @@
         <v>29</v>
       </c>
       <c r="AI15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ15" t="n">
         <v>21</v>
@@ -3147,10 +3214,10 @@
         <v>30</v>
       </c>
       <c r="AR15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT15" t="n">
         <v>4</v>
@@ -3159,16 +3226,16 @@
         <v>17</v>
       </c>
       <c r="AV15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW15" t="n">
         <v>25</v>
       </c>
       <c r="AX15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ15" t="n">
         <v>2</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -3287,10 +3354,10 @@
         <v>4.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF16" t="n">
         <v>5</v>
@@ -3320,13 +3387,13 @@
         <v>23</v>
       </c>
       <c r="AO16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR16" t="n">
         <v>4</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -3391,37 +3458,37 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E17" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F17" t="n">
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.795</v>
+        <v>0.792</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
       </c>
       <c r="I17" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="J17" t="n">
-        <v>77.7</v>
+        <v>77.8</v>
       </c>
       <c r="K17" t="n">
-        <v>0.494</v>
+        <v>0.495</v>
       </c>
       <c r="L17" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="M17" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.394</v>
+        <v>0.393</v>
       </c>
       <c r="O17" t="n">
         <v>17.3</v>
@@ -3430,22 +3497,22 @@
         <v>22.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.762</v>
+        <v>0.761</v>
       </c>
       <c r="R17" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T17" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="U17" t="n">
         <v>22.9</v>
       </c>
       <c r="V17" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="W17" t="n">
         <v>8.800000000000001</v>
@@ -3454,7 +3521,7 @@
         <v>5.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Z17" t="n">
         <v>18.7</v>
@@ -3466,10 +3533,10 @@
         <v>102.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3484,7 +3551,7 @@
         <v>4</v>
       </c>
       <c r="AI17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3505,7 +3572,7 @@
         <v>12</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
         <v>14</v>
@@ -3514,13 +3581,13 @@
         <v>28</v>
       </c>
       <c r="AS17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV17" t="n">
         <v>4</v>
@@ -3529,7 +3596,7 @@
         <v>3</v>
       </c>
       <c r="AX17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -3573,64 +3640,64 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E18" t="n">
         <v>37</v>
       </c>
       <c r="F18" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G18" t="n">
-        <v>0.474</v>
+        <v>0.481</v>
       </c>
       <c r="H18" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I18" t="n">
         <v>38.2</v>
       </c>
       <c r="J18" t="n">
-        <v>87.59999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="L18" t="n">
         <v>7.1</v>
       </c>
       <c r="M18" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0.358</v>
+        <v>0.359</v>
       </c>
       <c r="O18" t="n">
         <v>15.4</v>
       </c>
       <c r="P18" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.738</v>
+        <v>0.74</v>
       </c>
       <c r="R18" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="S18" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T18" t="n">
-        <v>43.9</v>
+        <v>43.7</v>
       </c>
       <c r="U18" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V18" t="n">
         <v>14.1</v>
       </c>
       <c r="W18" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X18" t="n">
         <v>6.8</v>
@@ -3645,13 +3712,13 @@
         <v>19.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.90000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE18" t="n">
         <v>18</v>
@@ -3663,10 +3730,10 @@
         <v>18</v>
       </c>
       <c r="AH18" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AI18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ18" t="n">
         <v>1</v>
@@ -3681,7 +3748,7 @@
         <v>14</v>
       </c>
       <c r="AN18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO18" t="n">
         <v>25</v>
@@ -3702,19 +3769,19 @@
         <v>5</v>
       </c>
       <c r="AU18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AV18" t="n">
         <v>9</v>
       </c>
       <c r="AW18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX18" t="n">
         <v>2</v>
       </c>
       <c r="AY18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ18" t="n">
         <v>9</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E19" t="n">
         <v>29</v>
       </c>
       <c r="F19" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G19" t="n">
-        <v>0.372</v>
+        <v>0.377</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
@@ -3773,10 +3840,10 @@
         <v>35.8</v>
       </c>
       <c r="J19" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L19" t="n">
         <v>5.4</v>
@@ -3785,16 +3852,16 @@
         <v>17.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.303</v>
+        <v>0.304</v>
       </c>
       <c r="O19" t="n">
         <v>18.6</v>
       </c>
       <c r="P19" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.738</v>
+        <v>0.736</v>
       </c>
       <c r="R19" t="n">
         <v>12.1</v>
@@ -3824,22 +3891,22 @@
         <v>18.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AB19" t="n">
         <v>95.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.5</v>
+        <v>-2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE19" t="n">
         <v>22</v>
       </c>
       <c r="AF19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG19" t="n">
         <v>22</v>
@@ -3851,7 +3918,7 @@
         <v>25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -3875,10 +3942,10 @@
         <v>22</v>
       </c>
       <c r="AR19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT19" t="n">
         <v>13</v>
@@ -3890,16 +3957,16 @@
         <v>20</v>
       </c>
       <c r="AW19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX19" t="n">
         <v>18</v>
       </c>
       <c r="AY19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
@@ -3908,7 +3975,7 @@
         <v>20</v>
       </c>
       <c r="BC19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -3937,28 +4004,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E20" t="n">
         <v>27</v>
       </c>
       <c r="F20" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G20" t="n">
-        <v>0.342</v>
+        <v>0.346</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J20" t="n">
         <v>80.2</v>
       </c>
       <c r="K20" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L20" t="n">
         <v>6.5</v>
@@ -3970,10 +4037,10 @@
         <v>0.363</v>
       </c>
       <c r="O20" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="P20" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="Q20" t="n">
         <v>0.781</v>
@@ -4003,22 +4070,22 @@
         <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>94.2</v>
+        <v>94</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.6</v>
+        <v>-3.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF20" t="n">
         <v>25</v>
@@ -4030,7 +4097,7 @@
         <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ20" t="n">
         <v>26</v>
@@ -4045,13 +4112,13 @@
         <v>21</v>
       </c>
       <c r="AN20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO20" t="n">
         <v>26</v>
       </c>
       <c r="AP20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ20" t="n">
         <v>6</v>
@@ -4063,7 +4130,7 @@
         <v>26</v>
       </c>
       <c r="AT20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU20" t="n">
         <v>23</v>
@@ -4075,16 +4142,16 @@
         <v>30</v>
       </c>
       <c r="AX20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ20" t="n">
         <v>19</v>
       </c>
       <c r="BA20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -4197,16 +4264,16 @@
         <v>4.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="AE21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF21" t="n">
         <v>6</v>
       </c>
       <c r="AG21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH21" t="n">
         <v>30</v>
@@ -4236,10 +4303,10 @@
         <v>16</v>
       </c>
       <c r="AQ21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS21" t="n">
         <v>24</v>
@@ -4254,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4269,7 +4336,7 @@
         <v>19</v>
       </c>
       <c r="BB21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC21" t="n">
         <v>7</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -4379,19 +4446,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI22" t="n">
         <v>8</v>
@@ -4436,7 +4503,7 @@
         <v>28</v>
       </c>
       <c r="AW22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
@@ -4448,10 +4515,10 @@
         <v>18</v>
       </c>
       <c r="BA22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -4483,28 +4550,28 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F23" t="n">
         <v>59</v>
       </c>
       <c r="G23" t="n">
-        <v>0.253</v>
+        <v>0.244</v>
       </c>
       <c r="H23" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.8</v>
+        <v>37.6</v>
       </c>
       <c r="J23" t="n">
-        <v>84.40000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L23" t="n">
         <v>6.3</v>
@@ -4513,28 +4580,28 @@
         <v>19</v>
       </c>
       <c r="N23" t="n">
-        <v>0.332</v>
+        <v>0.33</v>
       </c>
       <c r="O23" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="P23" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.764</v>
+        <v>0.766</v>
       </c>
       <c r="R23" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S23" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="T23" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="U23" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V23" t="n">
         <v>14.4</v>
@@ -4546,7 +4613,7 @@
         <v>4.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z23" t="n">
         <v>19.5</v>
@@ -4555,13 +4622,13 @@
         <v>16.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.3</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.5</v>
+        <v>-6.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4573,16 +4640,16 @@
         <v>29</v>
       </c>
       <c r="AH23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI23" t="n">
         <v>10</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL23" t="n">
         <v>21</v>
@@ -4603,7 +4670,7 @@
         <v>12</v>
       </c>
       <c r="AR23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AS23" t="n">
         <v>9</v>
@@ -4612,7 +4679,7 @@
         <v>11</v>
       </c>
       <c r="AU23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AV23" t="n">
         <v>11</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E24" t="n">
         <v>31</v>
       </c>
       <c r="F24" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G24" t="n">
-        <v>0.397</v>
+        <v>0.403</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
@@ -4683,7 +4750,7 @@
         <v>37.2</v>
       </c>
       <c r="J24" t="n">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K24" t="n">
         <v>0.443</v>
@@ -4692,19 +4759,19 @@
         <v>6.3</v>
       </c>
       <c r="M24" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0.361</v>
+        <v>0.362</v>
       </c>
       <c r="O24" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="P24" t="n">
         <v>16.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.727</v>
+        <v>0.723</v>
       </c>
       <c r="R24" t="n">
         <v>10.9</v>
@@ -4725,10 +4792,10 @@
         <v>7.3</v>
       </c>
       <c r="X24" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z24" t="n">
         <v>18.5</v>
@@ -4737,13 +4804,13 @@
         <v>16.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>92.90000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.9</v>
+        <v>-3.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -4755,7 +4822,7 @@
         <v>20</v>
       </c>
       <c r="AH24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
         <v>16</v>
@@ -4773,7 +4840,7 @@
         <v>25</v>
       </c>
       <c r="AN24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F25" t="n">
         <v>55</v>
       </c>
       <c r="G25" t="n">
-        <v>0.304</v>
+        <v>0.295</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
@@ -4871,13 +4938,13 @@
         <v>0.442</v>
       </c>
       <c r="L25" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M25" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0.329</v>
+        <v>0.327</v>
       </c>
       <c r="O25" t="n">
         <v>14.7</v>
@@ -4886,7 +4953,7 @@
         <v>19.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.744</v>
+        <v>0.742</v>
       </c>
       <c r="R25" t="n">
         <v>11.7</v>
@@ -4895,40 +4962,40 @@
         <v>29.9</v>
       </c>
       <c r="T25" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U25" t="n">
         <v>22.4</v>
       </c>
       <c r="V25" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W25" t="n">
         <v>8</v>
       </c>
       <c r="X25" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y25" t="n">
         <v>5</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA25" t="n">
         <v>18.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>94.90000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>-6.4</v>
+        <v>-6.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF25" t="n">
         <v>28</v>
@@ -4937,10 +5004,10 @@
         <v>28</v>
       </c>
       <c r="AH25" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AI25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ25" t="n">
         <v>5</v>
@@ -4952,7 +5019,7 @@
         <v>26</v>
       </c>
       <c r="AM25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN25" t="n">
         <v>29</v>
@@ -4967,10 +5034,10 @@
         <v>20</v>
       </c>
       <c r="AR25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT25" t="n">
         <v>17</v>
@@ -4985,7 +5052,7 @@
         <v>15</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY25" t="n">
         <v>17</v>
@@ -4994,7 +5061,7 @@
         <v>22</v>
       </c>
       <c r="BA25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB25" t="n">
         <v>21</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -5029,19 +5096,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E26" t="n">
         <v>33</v>
       </c>
       <c r="F26" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G26" t="n">
-        <v>0.423</v>
+        <v>0.429</v>
       </c>
       <c r="H26" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I26" t="n">
         <v>36.8</v>
@@ -5059,7 +5126,7 @@
         <v>23.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
       <c r="O26" t="n">
         <v>16</v>
@@ -5068,46 +5135,46 @@
         <v>20.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.777</v>
+        <v>0.776</v>
       </c>
       <c r="R26" t="n">
         <v>10.8</v>
       </c>
       <c r="S26" t="n">
-        <v>30.2</v>
+        <v>30.4</v>
       </c>
       <c r="T26" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="U26" t="n">
         <v>21.8</v>
       </c>
       <c r="V26" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W26" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="X26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z26" t="n">
         <v>18.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.8</v>
+        <v>97.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.7</v>
+        <v>-2.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
@@ -5131,7 +5198,7 @@
         <v>14</v>
       </c>
       <c r="AL26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM26" t="n">
         <v>4</v>
@@ -5146,10 +5213,10 @@
         <v>24</v>
       </c>
       <c r="AQ26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS26" t="n">
         <v>16</v>
@@ -5161,7 +5228,7 @@
         <v>18</v>
       </c>
       <c r="AV26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW26" t="n">
         <v>28</v>
@@ -5170,7 +5237,7 @@
         <v>24</v>
       </c>
       <c r="AY26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ26" t="n">
         <v>7</v>
@@ -5179,7 +5246,7 @@
         <v>26</v>
       </c>
       <c r="BB26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC26" t="n">
         <v>22</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -5211,37 +5278,37 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F27" t="n">
         <v>50</v>
       </c>
       <c r="G27" t="n">
-        <v>0.359</v>
+        <v>0.351</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="J27" t="n">
         <v>83.8</v>
       </c>
       <c r="K27" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L27" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M27" t="n">
         <v>20.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0.363</v>
+        <v>0.361</v>
       </c>
       <c r="O27" t="n">
         <v>17.7</v>
@@ -5256,13 +5323,13 @@
         <v>11.5</v>
       </c>
       <c r="S27" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="T27" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="U27" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V27" t="n">
         <v>14.7</v>
@@ -5271,31 +5338,31 @@
         <v>8.1</v>
       </c>
       <c r="X27" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y27" t="n">
         <v>6.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA27" t="n">
         <v>20.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.6</v>
+        <v>-4.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
       </c>
       <c r="AF27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG27" t="n">
         <v>24</v>
@@ -5304,13 +5371,13 @@
         <v>12</v>
       </c>
       <c r="AI27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ27" t="n">
         <v>8</v>
       </c>
       <c r="AK27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL27" t="n">
         <v>11</v>
@@ -5319,7 +5386,7 @@
         <v>11</v>
       </c>
       <c r="AN27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AO27" t="n">
         <v>7</v>
@@ -5331,37 +5398,37 @@
         <v>11</v>
       </c>
       <c r="AR27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS27" t="n">
         <v>28</v>
       </c>
       <c r="AT27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU27" t="n">
         <v>25</v>
       </c>
       <c r="AV27" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AW27" t="n">
         <v>13</v>
       </c>
       <c r="AX27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY27" t="n">
         <v>27</v>
       </c>
       <c r="AZ27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA27" t="n">
         <v>12</v>
       </c>
       <c r="BB27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC27" t="n">
         <v>27</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E28" t="n">
         <v>57</v>
       </c>
       <c r="F28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G28" t="n">
-        <v>0.731</v>
+        <v>0.74</v>
       </c>
       <c r="H28" t="n">
         <v>48.5</v>
@@ -5411,10 +5478,10 @@
         <v>39.2</v>
       </c>
       <c r="J28" t="n">
-        <v>81.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.483</v>
+        <v>0.484</v>
       </c>
       <c r="L28" t="n">
         <v>8.199999999999999</v>
@@ -5423,19 +5490,19 @@
         <v>21.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0.377</v>
+        <v>0.379</v>
       </c>
       <c r="O28" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="P28" t="n">
         <v>21.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.79</v>
+        <v>0.791</v>
       </c>
       <c r="R28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="S28" t="n">
         <v>33.1</v>
@@ -5462,16 +5529,16 @@
         <v>17.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.2</v>
+        <v>103.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5495,7 +5562,7 @@
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM28" t="n">
         <v>7</v>
@@ -5507,7 +5574,7 @@
         <v>15</v>
       </c>
       <c r="AP28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
         <v>4</v>
@@ -5516,10 +5583,10 @@
         <v>29</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
@@ -5534,13 +5601,13 @@
         <v>10</v>
       </c>
       <c r="AY28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB28" t="n">
         <v>4</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
         <v>21</v>
@@ -5671,7 +5738,7 @@
         <v>21</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK29" t="n">
         <v>21</v>
@@ -5716,7 +5783,7 @@
         <v>19</v>
       </c>
       <c r="AY29" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -5838,13 +5905,13 @@
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH30" t="n">
         <v>7</v>
@@ -5859,16 +5926,16 @@
         <v>12</v>
       </c>
       <c r="AL30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM30" t="n">
         <v>27</v>
       </c>
       <c r="AN30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP30" t="n">
         <v>10</v>
@@ -5880,7 +5947,7 @@
         <v>8</v>
       </c>
       <c r="AS30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT30" t="n">
         <v>15</v>
@@ -5910,7 +5977,7 @@
         <v>13</v>
       </c>
       <c r="BC30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E31" t="n">
         <v>29</v>
       </c>
       <c r="F31" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G31" t="n">
-        <v>0.367</v>
+        <v>0.372</v>
       </c>
       <c r="H31" t="n">
         <v>48.4</v>
@@ -5969,7 +6036,7 @@
         <v>18.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.366</v>
+        <v>0.365</v>
       </c>
       <c r="O31" t="n">
         <v>15.7</v>
@@ -5978,16 +6045,16 @@
         <v>21.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.733</v>
+        <v>0.734</v>
       </c>
       <c r="R31" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S31" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T31" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U31" t="n">
         <v>21.7</v>
@@ -5996,7 +6063,7 @@
         <v>15.1</v>
       </c>
       <c r="W31" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X31" t="n">
         <v>4.5</v>
@@ -6017,7 +6084,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE31" t="n">
         <v>22</v>
@@ -6041,22 +6108,22 @@
         <v>28</v>
       </c>
       <c r="AL31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM31" t="n">
         <v>20</v>
       </c>
       <c r="AN31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP31" t="n">
         <v>18</v>
       </c>
       <c r="AQ31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR31" t="n">
         <v>20</v>
@@ -6065,25 +6132,25 @@
         <v>7</v>
       </c>
       <c r="AT31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU31" t="n">
         <v>19</v>
       </c>
       <c r="AV31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW31" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX31" t="n">
         <v>23</v>
       </c>
       <c r="AY31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA31" t="n">
         <v>23</v>
@@ -6092,7 +6159,7 @@
         <v>27</v>
       </c>
       <c r="BC31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-10-2012-13</t>
+          <t>2013-04-10</t>
         </is>
       </c>
     </row>
